--- a/ressources/grc-asset-inventory-template-pme.xlsx
+++ b/ressources/grc-asset-inventory-template-pme.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="205">
   <si>
     <t>Ce document a été exporté depuis Numbers. Chaque tableau a été converti en feuille de calcul Excel. Tous les autres objets sur chaque feuille Numbers ont été placés sur des feuilles de calcul différentes. Veuillez noter que les calculs de formules peuvent être différents dans Excel.</t>
   </si>
@@ -51,10 +51,78 @@
     <t>Nom de la feuille de calcul Excel</t>
   </si>
   <si>
+    <t>Résumé de l’exportation</t>
+  </si>
+  <si>
+    <t>Tableau 1</t>
+  </si>
+  <si>
     <t>Mode d'emploi</t>
   </si>
   <si>
     <t>Sommaire et mode d’emploi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>Mode d'emploi - Sommaire et mod</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Inventaire des actifs</t>
+  </si>
+  <si>
+    <t>Inventaire des actifs et Matrice des Risques 3*3 - Adapté PME</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>1. Inventaire des actifs - Inve</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Grille de Scoring</t>
+  </si>
+  <si>
+    <t>Grille de Scoring PME - Critères d’Impact, Probabilité et Risque+ Décisions de Traitement</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>2. Grille de Scoring - Grille d</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Mapping des risques</t>
+  </si>
+  <si>
+    <t>Mapping des risques - Adapté PME: Top Risques Identifiés</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>3. Mapping des risques - Mappin</t>
+    </r>
   </si>
   <si>
     <t>Mode d'emploi - Sommaire et mod</t>
@@ -260,14 +328,50 @@
     <t>Disclaimer</t>
   </si>
   <si>
-    <t>Outil de travail pour audit GRC de petites PME: inventaire des actifs, grille de cotation des risques (3*3) et mapping des risques. Outil non contractuel ne remplaçant pas le recours à des professionnels.
-A noter: des exemples sont fournis pour illustrer la démarche et les choix possibles.</t>
-  </si>
-  <si>
-    <t>1. Inventaire des actifs</t>
-  </si>
-  <si>
-    <t>Inventaire des actifs et Matrice des Risques 3*3 - Adapté PME</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Outil de travail pour audit GRC de petites PME: inventaire des actifs, grille de cotation des risques (3*3) et mapping des risques. Outil non contractuel ne remplaçant pas le recours à des professionnels.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">A noter: des exemples sont fournis pour illustrer la démarche et les choix possibles.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times Roman"/>
+      </rPr>
+      <t xml:space="preserve">Licence : CC BY 4.0 — Attribution : Solène Figueiredo, projet </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="1"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times Roman"/>
+      </rPr>
+      <t>grc-pme-fictive</t>
+    </r>
   </si>
   <si>
     <t>1. Inventaire des actifs - Inve</t>
@@ -459,8 +563,16 @@
         <color indexed="8"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">- 1–2: acceptable  -- 3–5: remédiation sous 3 mois 
+      <t xml:space="preserve">- 1–2: acceptable 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">- 3–5: remédiation sous 3 mois 
 </t>
     </r>
     <r>
@@ -649,12 +761,6 @@
     <t>Utilisateur B2B</t>
   </si>
   <si>
-    <t>2. Grille de Scoring</t>
-  </si>
-  <si>
-    <t>Grille de Scoring PME - Critères d’Impact, Probabilité et Risque+ Décisions de Traitement</t>
-  </si>
-  <si>
     <t>2. Grille de Scoring - Grille d</t>
   </si>
   <si>
@@ -806,7 +912,7 @@
       <rPr>
         <b val="1"/>
         <sz val="14"/>
-        <color indexed="23"/>
+        <color indexed="25"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -841,12 +947,6 @@
   </si>
   <si>
     <t>Abandon d'une intégration non sécurisable</t>
-  </si>
-  <si>
-    <t>3. Mapping des risques</t>
-  </si>
-  <si>
-    <t>Mapping des risques - Adapté PME: Top Risques Identifiés</t>
   </si>
   <si>
     <t>3. Mapping des risques - Mappin</t>
@@ -1005,15 +1105,9 @@
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="59" formatCode="0,00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
@@ -1031,6 +1125,17 @@
       <u val="single"/>
       <sz val="12"/>
       <color indexed="11"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
@@ -1070,6 +1175,17 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Times Roman"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Times Roman"/>
+    </font>
+    <font>
       <i val="1"/>
       <sz val="10"/>
       <color indexed="8"/>
@@ -1091,7 +1207,7 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
-      <color indexed="23"/>
+      <color indexed="25"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1100,7 +1216,7 @@
       <name val="Helvetica Neue"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1121,7 +1237,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="12"/>
+        <fgColor indexed="13"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -1133,13 +1249,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="20"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="21"/>
+        <fgColor indexed="17"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -1149,8 +1259,20 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="23"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="24"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -1160,28 +1282,109 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="12"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="12"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="12"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color indexed="13"/>
+        <color indexed="12"/>
       </right>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="12"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="12"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="12"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="12"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="12"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="12"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="12"/>
       </left>
-      <right style="thin">
-        <color indexed="13"/>
-      </right>
+      <right/>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="12"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="14"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="12"/>
       </top>
       <bottom style="thin">
         <color indexed="14"/>
@@ -1190,7 +1393,7 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </left>
       <right style="thin">
         <color indexed="14"/>
@@ -1199,7 +1402,7 @@
         <color indexed="14"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1208,43 +1411,54 @@
         <color indexed="14"/>
       </left>
       <right style="thin">
-        <color indexed="13"/>
+        <color indexed="12"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="14"/>
+      </left>
+      <right style="thin">
+        <color indexed="14"/>
       </right>
       <top style="thin">
         <color indexed="14"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </left>
       <right style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </right>
       <top style="thin">
-        <color indexed="14"/>
+        <color indexed="16"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </left>
       <right style="thin">
         <color indexed="14"/>
       </right>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1253,85 +1467,105 @@
         <color indexed="14"/>
       </left>
       <right style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </right>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </left>
       <right style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </left>
       <right style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="12"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="12"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="12"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="12"/>
       </left>
-      <right style="thin">
-        <color indexed="13"/>
-      </right>
+      <right/>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="12"/>
       </top>
       <bottom style="thin">
-        <color indexed="14"/>
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="12"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </right>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
         <color indexed="14"/>
@@ -1340,31 +1574,31 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </left>
       <right style="thin">
         <color indexed="14"/>
       </right>
       <top style="thin">
-        <color indexed="14"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </left>
       <right style="thin">
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="14"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1373,28 +1607,39 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
+        <color indexed="12"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
         <color indexed="14"/>
       </right>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </left>
       <right style="thin">
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1403,13 +1648,13 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="14"/>
+        <color indexed="16"/>
       </right>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </top>
       <bottom style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1418,55 +1663,55 @@
         <color indexed="14"/>
       </left>
       <right style="thin">
-        <color indexed="13"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </top>
       <bottom style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </right>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </top>
       <bottom style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </left>
       <right style="thin">
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </top>
       <bottom style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="14"/>
+        <color indexed="16"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -1475,13 +1720,13 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="14"/>
+        <color indexed="16"/>
       </left>
       <right style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -1490,13 +1735,13 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </left>
       <right style="thin">
-        <color indexed="13"/>
+        <color indexed="14"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -1505,16 +1750,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </left>
       <right style="thin">
-        <color indexed="14"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="14"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1523,13 +1768,123 @@
         <color indexed="14"/>
       </left>
       <right style="thin">
-        <color indexed="13"/>
+        <color indexed="16"/>
       </right>
       <top style="thin">
         <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="13"/>
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="16"/>
+      </left>
+      <right style="thin">
+        <color indexed="14"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="14"/>
+      </left>
+      <right style="thin">
+        <color indexed="14"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="16"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="14"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="16"/>
+      </left>
+      <right style="thin">
+        <color indexed="14"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="14"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="12"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="12"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="14"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="14"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="12"/>
+      </right>
+      <top style="thin">
+        <color indexed="14"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="12"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1539,293 +1894,389 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="59" fontId="8" fillId="5" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="5" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="59" fontId="9" fillId="6" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="8" fillId="6" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="4" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="5" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="30" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="31" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="35" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="36" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="38" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="39" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="40" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="41" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="5" borderId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="32" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="33" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="33" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="8" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="9" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="32" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="35" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="36" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="7" fillId="6" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="4" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="7" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="6" fillId="5" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="45" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="46" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1839,29 +2290,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="16"/>
-          <bgColor indexed="17"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="16"/>
-          <bgColor indexed="18"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="16"/>
+          <fgColor indexed="18"/>
           <bgColor indexed="19"/>
         </patternFill>
       </fill>
@@ -1872,8 +2301,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="16"/>
-          <bgColor indexed="19"/>
+          <fgColor indexed="18"/>
+          <bgColor indexed="20"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1883,8 +2312,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="16"/>
-          <bgColor indexed="18"/>
+          <fgColor indexed="18"/>
+          <bgColor indexed="21"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1894,8 +2323,30 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="16"/>
-          <bgColor indexed="17"/>
+          <fgColor indexed="18"/>
+          <bgColor indexed="21"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="ff000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="18"/>
+          <bgColor indexed="20"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="ff000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="18"/>
+          <bgColor indexed="19"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1906,8 +2357,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="16"/>
-          <bgColor indexed="24"/>
+          <fgColor indexed="18"/>
+          <bgColor indexed="26"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1918,15 +2369,15 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="16"/>
-          <bgColor indexed="26"/>
+          <fgColor indexed="18"/>
+          <bgColor indexed="28"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00000000"/>
+        <color rgb="ff000000"/>
       </font>
     </dxf>
   </dxfs>
@@ -1945,14 +2396,16 @@
       <rgbColor rgb="ff5e88b1"/>
       <rgbColor rgb="ffeef3f4"/>
       <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ffbdc0bf"/>
-      <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ff3f3f3f"/>
       <rgbColor rgb="ffdbdbdb"/>
       <rgbColor rgb="00000000"/>
-      <rgbColor rgb="e5afe489"/>
-      <rgbColor rgb="e5fffc98"/>
-      <rgbColor rgb="e5ff9781"/>
+      <rgbColor rgb="ffafe489"/>
+      <rgbColor rgb="fffffc98"/>
+      <rgbColor rgb="ffff9781"/>
       <rgbColor rgb="ff88f94e"/>
       <rgbColor rgb="ffffd931"/>
       <rgbColor rgb="fffe634d"/>
@@ -1976,10 +2429,10 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="5E5E5E"/>
+        <a:srgbClr val="A7A7A7"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="D5D5D5"/>
+        <a:srgbClr val="535353"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="00A2FF"/>
@@ -2156,11 +2609,14 @@
     <a:spDef>
       <a:spPr>
         <a:solidFill>
-          <a:srgbClr val="000000"/>
+          <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:miter lim="400000"/>
+        <a:ln w="25400" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -2169,7 +2625,7 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="584200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2183,19 +2639,19 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
             <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Helvetica Neue Medium"/>
-            <a:ea typeface="Helvetica Neue Medium"/>
-            <a:cs typeface="Helvetica Neue Medium"/>
-            <a:sym typeface="Helvetica Neue Medium"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -2434,12 +2890,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
-            <a:srgbClr val="000000"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="400000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -2720,7 +3176,7 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="457200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2988,104 +3444,203 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="1" max="1" width="2" style="6" customWidth="1"/>
     <col min="2" max="4" width="33.6016" customWidth="1"/>
+    <col min="2" max="2" width="33.6719" style="6" customWidth="1"/>
+    <col min="3" max="3" width="33.6719" style="6" customWidth="1"/>
+    <col min="4" max="4" width="33.6719" style="6" customWidth="1"/>
+    <col min="5" max="5" width="10" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="10" style="6" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" ht="14.7" customHeight="1">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="9"/>
+    </row>
+    <row r="2" ht="14.7" customHeight="1">
+      <c r="A2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="12"/>
+    </row>
     <row r="3" ht="50" customHeight="1">
-      <c r="B3" t="s" s="1">
+      <c r="A3" s="10"/>
+      <c r="B3" t="s" s="13">
         <v>0</v>
       </c>
-      <c r="C3"/>
-      <c r="D3"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="12"/>
+    </row>
+    <row r="4" ht="14.7" customHeight="1">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+    </row>
+    <row r="5" ht="14.7" customHeight="1">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+    </row>
+    <row r="6" ht="14.7" customHeight="1">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="12"/>
     </row>
     <row r="7">
-      <c r="B7" t="s" s="2">
+      <c r="A7" s="10"/>
+      <c r="B7" t="s" s="14">
         <v>1</v>
       </c>
-      <c r="C7" t="s" s="2">
+      <c r="C7" t="s" s="14">
         <v>2</v>
       </c>
-      <c r="D7" t="s" s="2">
+      <c r="D7" t="s" s="14">
         <v>3</v>
       </c>
+      <c r="E7" s="12"/>
+    </row>
+    <row r="8" ht="14.7" customHeight="1">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="12"/>
     </row>
     <row r="9">
-      <c r="B9" t="s" s="3">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="A9" s="10"/>
+      <c r="B9" t="s" s="15">
+        <v>6</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="12"/>
     </row>
     <row r="10">
-      <c r="B10" s="4"/>
-      <c r="C10" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="A10" s="10"/>
+      <c r="B10" s="17"/>
+      <c r="C10" t="s" s="18">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s" s="19">
+        <v>8</v>
+      </c>
+      <c r="E10" s="12"/>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="10"/>
       <c r="B11" t="s" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-    </row>
-    <row r="12">
+      <c r="E11" s="12"/>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="10"/>
       <c r="B12" s="4"/>
       <c r="C12" t="s" s="4">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D12" t="s" s="5">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>18</v>
+      </c>
+      <c r="E12" s="12"/>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="10"/>
       <c r="B13" t="s" s="3">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14">
+      <c r="E13" s="12"/>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="10"/>
       <c r="B14" s="4"/>
       <c r="C14" t="s" s="4">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s" s="5">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>37</v>
+      </c>
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="10"/>
       <c r="B15" t="s" s="3">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
-    </row>
-    <row r="16">
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="20"/>
       <c r="B16" s="4"/>
       <c r="C16" t="s" s="4">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="D16" t="s" s="5">
-        <v>155</v>
+        <v>107</v>
+      </c>
+      <c r="E16" s="24"/>
+    </row>
+    <row r="17">
+      <c r="B17" t="s" s="3">
+        <v>161</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="4"/>
+      <c r="C18" t="s" s="4">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s" s="5">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D10" location="'Mode d''emploi - Sommaire et mod'!R2C1" tooltip="" display="Mode d'emploi - Sommaire et mod"/>
-    <hyperlink ref="D12" location="'1. Inventaire des actifs - Inve'!R2C1" tooltip="" display="1. Inventaire des actifs - Inve"/>
-    <hyperlink ref="D14" location="'2. Grille de Scoring - Grille d'!R2C1" tooltip="" display="2. Grille de Scoring - Grille d"/>
-    <hyperlink ref="D16" location="'3. Mapping des risques - Mappin'!R2C1" tooltip="" display="3. Mapping des risques - Mappin"/>
+    <hyperlink ref="D10" location="'Résumé de l’exportation'!R1C1" tooltip="" display="Résumé de l’exportation"/>
+    <hyperlink ref="D10" location="'Mode d''emploi - Sommaire et mod'!R1C1" tooltip="" display="Mode d'emploi - Sommaire et mod"/>
+    <hyperlink ref="D12" location="'1. Inventaire des actifs - Inve'!R1C1" tooltip="" display="1. Inventaire des actifs - Inve"/>
+    <hyperlink ref="D14" location="'2. Grille de Scoring - Grille d'!R1C1" tooltip="" display="2. Grille de Scoring - Grille d"/>
+    <hyperlink ref="D16" location="'3. Mapping des risques - Mappin'!R1C1" tooltip="" display="3. Mapping des risques - Mappin"/>
+    <hyperlink ref="D12" location="'Mode d''emploi - Sommaire et mod'!R1C1" tooltip="" display="Mode d'emploi - Sommaire et mod"/>
+    <hyperlink ref="D14" location="'1. Inventaire des actifs - Inve'!R1C1" tooltip="" display="1. Inventaire des actifs - Inve"/>
+    <hyperlink ref="D16" location="'2. Grille de Scoring - Grille d'!R1C1" tooltip="" display="2. Grille de Scoring - Grille d"/>
+    <hyperlink ref="D18" location="'3. Mapping des risques - Mappin'!R1C1" tooltip="" display="3. Mapping des risques - Mappin"/>
   </hyperlinks>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3094,137 +3649,152 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="16.3516" style="6" customWidth="1"/>
-    <col min="2" max="2" width="25.0625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="45.4297" style="6" customWidth="1"/>
-    <col min="4" max="4" width="65.8281" style="6" customWidth="1"/>
-    <col min="5" max="16384" width="16.3516" style="6" customWidth="1"/>
+    <col min="1" max="1" width="16.3516" style="25" customWidth="1"/>
+    <col min="2" max="2" width="25" style="25" customWidth="1"/>
+    <col min="3" max="3" width="45.5" style="25" customWidth="1"/>
+    <col min="4" max="4" width="65.8516" style="25" customWidth="1"/>
+    <col min="5" max="5" width="16.3516" style="25" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.65" customHeight="1">
-      <c r="A1" t="s" s="7">
-        <v>5</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="A1" t="s" s="26">
+        <v>7</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="28"/>
     </row>
     <row r="2" ht="35.95" customHeight="1">
-      <c r="A2" t="s" s="8">
-        <v>7</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="A2" t="s" s="29">
+        <v>19</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="31"/>
     </row>
     <row r="3" ht="74" customHeight="1">
-      <c r="A3" t="s" s="10">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s" s="10">
-        <v>9</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
+      <c r="A3" t="s" s="32">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s" s="32">
+        <v>21</v>
+      </c>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
     </row>
     <row r="4" ht="19.2" customHeight="1">
-      <c r="A4" t="s" s="11">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s" s="11">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s" s="11">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s" s="11">
-        <v>13</v>
-      </c>
+      <c r="A4" t="s" s="33">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s" s="33">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s" s="33">
+        <v>25</v>
+      </c>
+      <c r="E4" s="31"/>
     </row>
     <row r="5" ht="63.2" customHeight="1">
-      <c r="A5" s="12"/>
-      <c r="B5" t="s" s="13">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s" s="14">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s" s="14">
-        <v>16</v>
-      </c>
+      <c r="A5" s="34"/>
+      <c r="B5" t="s" s="35">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s" s="36">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s" s="36">
+        <v>28</v>
+      </c>
+      <c r="E5" s="31"/>
     </row>
     <row r="6" ht="74" customHeight="1">
-      <c r="A6" s="15"/>
-      <c r="B6" t="s" s="16">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s" s="17">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s" s="17">
-        <v>19</v>
-      </c>
+      <c r="A6" s="37"/>
+      <c r="B6" t="s" s="38">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s" s="39">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s" s="39">
+        <v>31</v>
+      </c>
+      <c r="E6" s="31"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="15"/>
-      <c r="B7" t="s" s="16">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s" s="18">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s" s="17">
-        <v>22</v>
-      </c>
+      <c r="A7" s="37"/>
+      <c r="B7" t="s" s="38">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s" s="40">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s" s="39">
+        <v>34</v>
+      </c>
+      <c r="E7" s="31"/>
     </row>
     <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="15"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-    </row>
-    <row r="9" ht="41" customHeight="1">
-      <c r="A9" t="s" s="21">
-        <v>23</v>
-      </c>
-      <c r="B9" t="s" s="16">
-        <v>24</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
+      <c r="A8" s="37"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="31"/>
+    </row>
+    <row r="9" ht="61" customHeight="1">
+      <c r="A9" t="s" s="43">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s" s="38">
+        <v>36</v>
+      </c>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="31"/>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="15"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="31"/>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="15"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="31"/>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="15"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="31"/>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="15"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="31"/>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="15"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3234,9 +3804,9 @@
     <mergeCell ref="B9:D9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B5" location="'1. Inventaire des actifs - Inve'!R2C1" tooltip="" display="1. Inventaire des actifs"/>
-    <hyperlink ref="B6" location="'2. Grille de Scoring - Grille d'!R2C1" tooltip="" display="2. Grille de scoring"/>
-    <hyperlink ref="B7" location="'3. Mapping des risques - Mappin'!R2C1" tooltip="" display="3. Mapping des risques"/>
+    <hyperlink ref="B5" location="'1. Inventaire des actifs - Inve'!R1C1" tooltip="" display="1. Inventaire des actifs"/>
+    <hyperlink ref="B6" location="'2. Grille de Scoring - Grille d'!R1C1" tooltip="" display="2. Grille de scoring"/>
+    <hyperlink ref="B7" location="'3. Mapping des risques - Mappin'!R1C1" tooltip="" display="3. Mapping des risques"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -3251,819 +3821,819 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:I28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="6.44531" style="23" customWidth="1"/>
-    <col min="2" max="9" width="16.3516" style="23" customWidth="1"/>
-    <col min="10" max="16384" width="16.3516" style="23" customWidth="1"/>
+    <col min="1" max="1" width="6.5" style="46" customWidth="1"/>
+    <col min="2" max="9" width="16.3516" style="46" customWidth="1"/>
+    <col min="10" max="16384" width="16.3516" style="46" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.6" customHeight="1">
-      <c r="A1" t="s" s="24">
-        <v>26</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="A1" t="s" s="47">
+        <v>10</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="49"/>
     </row>
     <row r="2" ht="30.2" customHeight="1">
-      <c r="A2" t="s" s="11">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s" s="11">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s" s="11">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s" s="11">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s" s="11">
-        <v>32</v>
-      </c>
-      <c r="F2" t="s" s="11">
-        <v>33</v>
-      </c>
-      <c r="G2" t="s" s="11">
-        <v>34</v>
-      </c>
-      <c r="H2" t="s" s="11">
-        <v>35</v>
-      </c>
-      <c r="I2" t="s" s="11">
-        <v>36</v>
+      <c r="A2" t="s" s="33">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s" s="33">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s" s="33">
+        <v>40</v>
+      </c>
+      <c r="D2" t="s" s="33">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s" s="33">
+        <v>42</v>
+      </c>
+      <c r="F2" t="s" s="33">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s" s="33">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s" s="33">
+        <v>45</v>
+      </c>
+      <c r="I2" t="s" s="33">
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="85.2" customHeight="1">
-      <c r="A3" t="s" s="25">
-        <v>37</v>
-      </c>
-      <c r="B3" t="s" s="26">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s" s="27">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s" s="28">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s" s="28">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s" s="28">
-        <v>42</v>
-      </c>
-      <c r="G3" t="s" s="28">
-        <v>43</v>
-      </c>
-      <c r="H3" t="s" s="28">
-        <v>43</v>
-      </c>
-      <c r="I3" t="s" s="29">
-        <v>44</v>
+      <c r="A3" t="s" s="50">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s" s="51">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s" s="52">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s" s="53">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s" s="53">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s" s="53">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s" s="53">
+        <v>53</v>
+      </c>
+      <c r="H3" t="s" s="53">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s" s="54">
+        <v>54</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="30">
+      <c r="A4" s="55">
         <v>1</v>
       </c>
-      <c r="B4" t="s" s="31">
-        <v>45</v>
-      </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="34" cm="1">
+      <c r="B4" t="s" s="56">
+        <v>55</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="59" cm="1">
         <f t="array" ref="I4">G4*H4</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="35">
+      <c r="A5" s="60">
         <v>2</v>
       </c>
-      <c r="B5" t="s" s="21">
-        <v>46</v>
-      </c>
-      <c r="C5" t="s" s="16">
-        <v>47</v>
-      </c>
-      <c r="D5" t="s" s="17">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s" s="17">
-        <v>49</v>
-      </c>
-      <c r="F5" t="s" s="17">
-        <v>50</v>
-      </c>
-      <c r="G5" s="36">
+      <c r="B5" t="s" s="43">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s" s="38">
+        <v>57</v>
+      </c>
+      <c r="D5" t="s" s="39">
+        <v>58</v>
+      </c>
+      <c r="E5" t="s" s="39">
+        <v>59</v>
+      </c>
+      <c r="F5" t="s" s="39">
+        <v>60</v>
+      </c>
+      <c r="G5" s="61">
         <v>3</v>
       </c>
-      <c r="H5" s="36">
+      <c r="H5" s="61">
         <v>2</v>
       </c>
-      <c r="I5" s="37" cm="1">
+      <c r="I5" s="62" cm="1">
         <f t="array" ref="I5">G5*H5</f>
         <v>6</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="35">
+      <c r="A6" s="60">
         <v>3</v>
       </c>
-      <c r="B6" t="s" s="21">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s" s="16">
-        <v>47</v>
-      </c>
-      <c r="D6" t="s" s="17">
-        <v>48</v>
-      </c>
-      <c r="E6" t="s" s="17">
-        <v>49</v>
-      </c>
-      <c r="F6" t="s" s="17">
-        <v>50</v>
-      </c>
-      <c r="G6" s="36">
+      <c r="B6" t="s" s="43">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s" s="38">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s" s="39">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s" s="39">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s" s="39">
+        <v>60</v>
+      </c>
+      <c r="G6" s="61">
         <v>3</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="61">
         <v>2</v>
       </c>
-      <c r="I6" s="37" cm="1">
+      <c r="I6" s="62" cm="1">
         <f t="array" ref="I6">G6*H6</f>
         <v>6</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="35">
+      <c r="A7" s="60">
         <v>4</v>
       </c>
-      <c r="B7" t="s" s="21">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s" s="16">
-        <v>47</v>
-      </c>
-      <c r="D7" t="s" s="17">
-        <v>48</v>
-      </c>
-      <c r="E7" t="s" s="17">
-        <v>53</v>
-      </c>
-      <c r="F7" t="s" s="17">
-        <v>54</v>
-      </c>
-      <c r="G7" s="36">
+      <c r="B7" t="s" s="43">
+        <v>62</v>
+      </c>
+      <c r="C7" t="s" s="38">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s" s="39">
+        <v>58</v>
+      </c>
+      <c r="E7" t="s" s="39">
+        <v>63</v>
+      </c>
+      <c r="F7" t="s" s="39">
+        <v>64</v>
+      </c>
+      <c r="G7" s="61">
         <v>3</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="61">
         <v>1</v>
       </c>
-      <c r="I7" s="37" cm="1">
+      <c r="I7" s="62" cm="1">
         <f t="array" ref="I7">G7*H7</f>
         <v>3</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="35">
+      <c r="A8" s="60">
         <v>5</v>
       </c>
-      <c r="B8" t="s" s="21">
-        <v>55</v>
-      </c>
-      <c r="C8" t="s" s="16">
-        <v>56</v>
-      </c>
-      <c r="D8" t="s" s="17">
-        <v>57</v>
-      </c>
-      <c r="E8" t="s" s="17">
-        <v>49</v>
-      </c>
-      <c r="F8" t="s" s="17">
-        <v>58</v>
-      </c>
-      <c r="G8" s="36">
+      <c r="B8" t="s" s="43">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s" s="38">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s" s="39">
+        <v>67</v>
+      </c>
+      <c r="E8" t="s" s="39">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s" s="39">
+        <v>68</v>
+      </c>
+      <c r="G8" s="61">
         <v>3</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="61">
         <v>2</v>
       </c>
-      <c r="I8" s="37" cm="1">
+      <c r="I8" s="62" cm="1">
         <f t="array" ref="I8">G8*H8</f>
         <v>6</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="35">
+      <c r="A9" s="60">
         <v>6</v>
       </c>
-      <c r="B9" t="s" s="21">
+      <c r="B9" t="s" s="43">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s" s="38">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s" s="39">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s" s="39">
         <v>59</v>
       </c>
-      <c r="C9" t="s" s="16">
-        <v>56</v>
-      </c>
-      <c r="D9" t="s" s="17">
-        <v>60</v>
-      </c>
-      <c r="E9" t="s" s="17">
-        <v>49</v>
-      </c>
-      <c r="F9" t="s" s="17">
-        <v>61</v>
-      </c>
-      <c r="G9" s="36">
+      <c r="F9" t="s" s="39">
+        <v>71</v>
+      </c>
+      <c r="G9" s="61">
         <v>3</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="61">
         <v>2</v>
       </c>
-      <c r="I9" s="37" cm="1">
+      <c r="I9" s="62" cm="1">
         <f t="array" ref="I9">G9*H9</f>
         <v>6</v>
       </c>
     </row>
     <row r="10" ht="41" customHeight="1">
-      <c r="A10" s="35">
+      <c r="A10" s="60">
         <v>7</v>
       </c>
-      <c r="B10" t="s" s="21">
-        <v>62</v>
-      </c>
-      <c r="C10" t="s" s="16">
-        <v>56</v>
-      </c>
-      <c r="D10" t="s" s="17">
-        <v>60</v>
-      </c>
-      <c r="E10" t="s" s="17">
-        <v>49</v>
-      </c>
-      <c r="F10" t="s" s="17">
-        <v>63</v>
-      </c>
-      <c r="G10" s="36">
+      <c r="B10" t="s" s="43">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s" s="38">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s" s="39">
+        <v>70</v>
+      </c>
+      <c r="E10" t="s" s="39">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s" s="39">
+        <v>73</v>
+      </c>
+      <c r="G10" s="61">
         <v>2</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="61">
         <v>2</v>
       </c>
-      <c r="I10" s="37" cm="1">
+      <c r="I10" s="62" cm="1">
         <f t="array" ref="I10">G10*H10</f>
         <v>4</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="35">
+      <c r="A11" s="60">
         <v>8</v>
       </c>
-      <c r="B11" t="s" s="21">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s" s="16">
-        <v>56</v>
-      </c>
-      <c r="D11" t="s" s="17">
-        <v>60</v>
-      </c>
-      <c r="E11" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F11" t="s" s="17">
+      <c r="B11" t="s" s="43">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s" s="38">
         <v>66</v>
       </c>
-      <c r="G11" s="36">
+      <c r="D11" t="s" s="39">
+        <v>70</v>
+      </c>
+      <c r="E11" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F11" t="s" s="39">
+        <v>76</v>
+      </c>
+      <c r="G11" s="61">
         <v>3</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="61">
         <v>2</v>
       </c>
-      <c r="I11" s="37" cm="1">
+      <c r="I11" s="62" cm="1">
         <f t="array" ref="I11">G11*H11</f>
         <v>6</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="35">
+      <c r="A12" s="60">
         <v>9</v>
       </c>
-      <c r="B12" t="s" s="21">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s" s="16">
-        <v>56</v>
-      </c>
-      <c r="D12" t="s" s="17">
-        <v>60</v>
-      </c>
-      <c r="E12" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F12" t="s" s="17">
-        <v>68</v>
-      </c>
-      <c r="G12" s="36">
+      <c r="B12" t="s" s="43">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s" s="38">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s" s="39">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F12" t="s" s="39">
+        <v>78</v>
+      </c>
+      <c r="G12" s="61">
         <v>3</v>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="61">
         <v>1</v>
       </c>
-      <c r="I12" s="37" cm="1">
+      <c r="I12" s="62" cm="1">
         <f t="array" ref="I12">G12*H12</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="35">
+      <c r="A13" s="60">
         <v>10</v>
       </c>
-      <c r="B13" t="s" s="21">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s" s="16">
-        <v>56</v>
-      </c>
-      <c r="D13" t="s" s="17">
-        <v>70</v>
-      </c>
-      <c r="E13" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F13" t="s" s="17">
-        <v>71</v>
-      </c>
-      <c r="G13" s="36">
+      <c r="B13" t="s" s="43">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s" s="38">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s" s="39">
+        <v>80</v>
+      </c>
+      <c r="E13" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s" s="39">
+        <v>81</v>
+      </c>
+      <c r="G13" s="61">
         <v>2</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="61">
         <v>1</v>
       </c>
-      <c r="I13" s="37" cm="1">
+      <c r="I13" s="62" cm="1">
         <f t="array" ref="I13">G13*H13</f>
         <v>2</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="35">
+      <c r="A14" s="60">
         <v>11</v>
       </c>
-      <c r="B14" t="s" s="21">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s" s="16">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s" s="17">
-        <v>70</v>
-      </c>
-      <c r="E14" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F14" t="s" s="17">
-        <v>71</v>
-      </c>
-      <c r="G14" s="36">
+      <c r="B14" t="s" s="43">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s" s="38">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s" s="39">
+        <v>80</v>
+      </c>
+      <c r="E14" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F14" t="s" s="39">
+        <v>81</v>
+      </c>
+      <c r="G14" s="61">
         <v>1</v>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="61">
         <v>1</v>
       </c>
-      <c r="I14" s="37" cm="1">
+      <c r="I14" s="62" cm="1">
         <f t="array" ref="I14">G14*H14</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="35">
+      <c r="A15" s="60">
         <v>12</v>
       </c>
-      <c r="B15" t="s" s="21">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s" s="16">
-        <v>56</v>
-      </c>
-      <c r="D15" t="s" s="17">
-        <v>70</v>
-      </c>
-      <c r="E15" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F15" t="s" s="17">
-        <v>71</v>
-      </c>
-      <c r="G15" s="36">
+      <c r="B15" t="s" s="43">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s" s="38">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s" s="39">
+        <v>80</v>
+      </c>
+      <c r="E15" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s" s="39">
+        <v>81</v>
+      </c>
+      <c r="G15" s="61">
         <v>1</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="61">
         <v>1</v>
       </c>
-      <c r="I15" s="37" cm="1">
+      <c r="I15" s="62" cm="1">
         <f t="array" ref="I15">G15*H15</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="35">
+      <c r="A16" s="60">
         <v>13</v>
       </c>
-      <c r="B16" t="s" s="21">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s" s="16">
-        <v>56</v>
-      </c>
-      <c r="D16" t="s" s="17">
-        <v>70</v>
-      </c>
-      <c r="E16" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F16" t="s" s="17">
-        <v>71</v>
-      </c>
-      <c r="G16" s="36">
+      <c r="B16" t="s" s="43">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s" s="38">
+        <v>66</v>
+      </c>
+      <c r="D16" t="s" s="39">
+        <v>80</v>
+      </c>
+      <c r="E16" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F16" t="s" s="39">
+        <v>81</v>
+      </c>
+      <c r="G16" s="61">
         <v>1</v>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="61">
         <v>1</v>
       </c>
-      <c r="I16" s="37" cm="1">
+      <c r="I16" s="62" cm="1">
         <f t="array" ref="I16">G16*H16</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" ht="41" customHeight="1">
-      <c r="A17" s="35">
+      <c r="A17" s="60">
         <v>14</v>
       </c>
-      <c r="B17" t="s" s="21">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s" s="16">
-        <v>76</v>
-      </c>
-      <c r="D17" t="s" s="17">
-        <v>77</v>
-      </c>
-      <c r="E17" t="s" s="17">
-        <v>49</v>
-      </c>
-      <c r="F17" t="s" s="17">
-        <v>78</v>
-      </c>
-      <c r="G17" s="36">
+      <c r="B17" t="s" s="43">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s" s="38">
+        <v>86</v>
+      </c>
+      <c r="D17" t="s" s="39">
+        <v>87</v>
+      </c>
+      <c r="E17" t="s" s="39">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s" s="39">
+        <v>88</v>
+      </c>
+      <c r="G17" s="61">
         <v>3</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="61">
         <v>2</v>
       </c>
-      <c r="I17" s="37" cm="1">
+      <c r="I17" s="62" cm="1">
         <f t="array" ref="I17">G17*H17</f>
         <v>6</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="35">
+      <c r="A18" s="60">
         <v>15</v>
       </c>
-      <c r="B18" t="s" s="21">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s" s="16">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s" s="17">
-        <v>77</v>
-      </c>
-      <c r="E18" t="s" s="17">
-        <v>49</v>
-      </c>
-      <c r="F18" t="s" s="17">
-        <v>80</v>
-      </c>
-      <c r="G18" s="36">
+      <c r="B18" t="s" s="43">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s" s="38">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s" s="39">
+        <v>87</v>
+      </c>
+      <c r="E18" t="s" s="39">
+        <v>59</v>
+      </c>
+      <c r="F18" t="s" s="39">
+        <v>90</v>
+      </c>
+      <c r="G18" s="61">
         <v>3</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="61">
         <v>2</v>
       </c>
-      <c r="I18" s="37" cm="1">
+      <c r="I18" s="62" cm="1">
         <f t="array" ref="I18">G18*H18</f>
         <v>6</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="35">
+      <c r="A19" s="60">
         <v>16</v>
       </c>
-      <c r="B19" t="s" s="21">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s" s="16">
-        <v>76</v>
-      </c>
-      <c r="D19" t="s" s="17">
-        <v>77</v>
-      </c>
-      <c r="E19" t="s" s="17">
-        <v>49</v>
-      </c>
-      <c r="F19" t="s" s="17">
-        <v>82</v>
-      </c>
-      <c r="G19" s="36">
+      <c r="B19" t="s" s="43">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s" s="38">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s" s="39">
+        <v>87</v>
+      </c>
+      <c r="E19" t="s" s="39">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s" s="39">
+        <v>92</v>
+      </c>
+      <c r="G19" s="61">
         <v>3</v>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="61">
         <v>2</v>
       </c>
-      <c r="I19" s="37" cm="1">
+      <c r="I19" s="62" cm="1">
         <f t="array" ref="I19">G19*H19</f>
         <v>6</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="35">
+      <c r="A20" s="60">
         <v>17</v>
       </c>
-      <c r="B20" t="s" s="21">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s" s="16">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s" s="17">
-        <v>77</v>
-      </c>
-      <c r="E20" t="s" s="17">
-        <v>53</v>
-      </c>
-      <c r="F20" t="s" s="17">
-        <v>52</v>
-      </c>
-      <c r="G20" s="36">
+      <c r="B20" t="s" s="43">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s" s="38">
+        <v>86</v>
+      </c>
+      <c r="D20" t="s" s="39">
+        <v>87</v>
+      </c>
+      <c r="E20" t="s" s="39">
+        <v>63</v>
+      </c>
+      <c r="F20" t="s" s="39">
+        <v>62</v>
+      </c>
+      <c r="G20" s="61">
         <v>1</v>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="61">
         <v>1</v>
       </c>
-      <c r="I20" s="37" cm="1">
+      <c r="I20" s="62" cm="1">
         <f t="array" ref="I20">G20*H20</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="35">
+      <c r="A21" s="60">
         <v>18</v>
       </c>
-      <c r="B21" t="s" s="21">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s" s="16">
-        <v>85</v>
-      </c>
-      <c r="D21" t="s" s="17">
-        <v>86</v>
-      </c>
-      <c r="E21" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F21" t="s" s="17">
-        <v>87</v>
-      </c>
-      <c r="G21" s="36">
+      <c r="B21" t="s" s="43">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s" s="38">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s" s="39">
+        <v>96</v>
+      </c>
+      <c r="E21" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F21" t="s" s="39">
+        <v>97</v>
+      </c>
+      <c r="G21" s="61">
         <v>3</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="61">
         <v>1</v>
       </c>
-      <c r="I21" s="37" cm="1">
+      <c r="I21" s="62" cm="1">
         <f t="array" ref="I21">G21*H21</f>
         <v>3</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="35">
+      <c r="A22" s="60">
         <v>19</v>
       </c>
-      <c r="B22" t="s" s="21">
-        <v>57</v>
-      </c>
-      <c r="C22" t="s" s="16">
-        <v>85</v>
-      </c>
-      <c r="D22" t="s" s="17">
-        <v>86</v>
-      </c>
-      <c r="E22" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F22" t="s" s="17">
-        <v>88</v>
-      </c>
-      <c r="G22" s="36">
+      <c r="B22" t="s" s="43">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s" s="38">
+        <v>95</v>
+      </c>
+      <c r="D22" t="s" s="39">
+        <v>96</v>
+      </c>
+      <c r="E22" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F22" t="s" s="39">
+        <v>98</v>
+      </c>
+      <c r="G22" s="61">
         <v>3</v>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="61">
         <v>1</v>
       </c>
-      <c r="I22" s="37" cm="1">
+      <c r="I22" s="62" cm="1">
         <f t="array" ref="I22">G22*H22</f>
         <v>3</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="35">
+      <c r="A23" s="60">
         <v>20</v>
       </c>
-      <c r="B23" t="s" s="21">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s" s="16">
-        <v>85</v>
-      </c>
-      <c r="D23" t="s" s="17">
-        <v>86</v>
-      </c>
-      <c r="E23" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F23" t="s" s="17">
-        <v>89</v>
-      </c>
-      <c r="G23" s="36">
+      <c r="B23" t="s" s="43">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s" s="38">
+        <v>95</v>
+      </c>
+      <c r="D23" t="s" s="39">
+        <v>96</v>
+      </c>
+      <c r="E23" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F23" t="s" s="39">
+        <v>99</v>
+      </c>
+      <c r="G23" s="61">
         <v>2</v>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="61">
         <v>1</v>
       </c>
-      <c r="I23" s="37" cm="1">
+      <c r="I23" s="62" cm="1">
         <f t="array" ref="I23">G23*H23</f>
         <v>2</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="35">
+      <c r="A24" s="60">
         <v>21</v>
       </c>
-      <c r="B24" t="s" s="21">
-        <v>48</v>
-      </c>
-      <c r="C24" t="s" s="16">
-        <v>85</v>
-      </c>
-      <c r="D24" t="s" s="17">
-        <v>86</v>
-      </c>
-      <c r="E24" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F24" t="s" s="17">
-        <v>90</v>
-      </c>
-      <c r="G24" s="36">
+      <c r="B24" t="s" s="43">
+        <v>58</v>
+      </c>
+      <c r="C24" t="s" s="38">
+        <v>95</v>
+      </c>
+      <c r="D24" t="s" s="39">
+        <v>96</v>
+      </c>
+      <c r="E24" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F24" t="s" s="39">
+        <v>100</v>
+      </c>
+      <c r="G24" s="61">
         <v>2</v>
       </c>
-      <c r="H24" s="36">
+      <c r="H24" s="61">
         <v>1</v>
       </c>
-      <c r="I24" s="37" cm="1">
+      <c r="I24" s="62" cm="1">
         <f t="array" ref="I24">G24*H24</f>
         <v>2</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="35">
+      <c r="A25" s="60">
         <v>22</v>
       </c>
-      <c r="B25" t="s" s="21">
-        <v>60</v>
-      </c>
-      <c r="C25" t="s" s="16">
-        <v>85</v>
-      </c>
-      <c r="D25" t="s" s="17">
-        <v>57</v>
-      </c>
-      <c r="E25" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F25" t="s" s="17">
-        <v>91</v>
-      </c>
-      <c r="G25" s="36">
+      <c r="B25" t="s" s="43">
+        <v>70</v>
+      </c>
+      <c r="C25" t="s" s="38">
+        <v>95</v>
+      </c>
+      <c r="D25" t="s" s="39">
+        <v>67</v>
+      </c>
+      <c r="E25" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F25" t="s" s="39">
+        <v>101</v>
+      </c>
+      <c r="G25" s="61">
         <v>2</v>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="61">
         <v>1</v>
       </c>
-      <c r="I25" s="37" cm="1">
+      <c r="I25" s="62" cm="1">
         <f t="array" ref="I25">G25*H25</f>
         <v>2</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="35">
+      <c r="A26" s="60">
         <v>23</v>
       </c>
-      <c r="B26" t="s" s="21">
-        <v>92</v>
-      </c>
-      <c r="C26" t="s" s="16">
-        <v>85</v>
-      </c>
-      <c r="D26" t="s" s="17">
-        <v>70</v>
-      </c>
-      <c r="E26" t="s" s="17">
-        <v>65</v>
-      </c>
-      <c r="F26" t="s" s="17">
-        <v>93</v>
-      </c>
-      <c r="G26" s="37">
+      <c r="B26" t="s" s="43">
+        <v>102</v>
+      </c>
+      <c r="C26" t="s" s="38">
+        <v>95</v>
+      </c>
+      <c r="D26" t="s" s="39">
+        <v>80</v>
+      </c>
+      <c r="E26" t="s" s="39">
+        <v>75</v>
+      </c>
+      <c r="F26" t="s" s="39">
+        <v>103</v>
+      </c>
+      <c r="G26" s="62">
         <v>1</v>
       </c>
-      <c r="H26" s="37">
+      <c r="H26" s="62">
         <v>1</v>
       </c>
-      <c r="I26" s="37" cm="1">
+      <c r="I26" s="62" cm="1">
         <f t="array" ref="I26">G26*H26</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="35">
+      <c r="A27" s="60">
         <v>24</v>
       </c>
-      <c r="B27" t="s" s="21">
-        <v>94</v>
-      </c>
-      <c r="C27" t="s" s="16">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s" s="17">
-        <v>48</v>
-      </c>
-      <c r="E27" t="s" s="17">
-        <v>49</v>
-      </c>
-      <c r="F27" t="s" s="17">
+      <c r="B27" t="s" s="43">
+        <v>104</v>
+      </c>
+      <c r="C27" t="s" s="38">
         <v>95</v>
       </c>
-      <c r="G27" s="37">
+      <c r="D27" t="s" s="39">
+        <v>58</v>
+      </c>
+      <c r="E27" t="s" s="39">
+        <v>59</v>
+      </c>
+      <c r="F27" t="s" s="39">
+        <v>105</v>
+      </c>
+      <c r="G27" s="62">
         <v>3</v>
       </c>
-      <c r="H27" s="37">
+      <c r="H27" s="62">
         <v>1</v>
       </c>
-      <c r="I27" s="37" cm="1">
+      <c r="I27" s="62" cm="1">
         <f t="array" ref="I27">G27*H27</f>
         <v>3</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="35">
+      <c r="A28" s="60">
         <v>25</v>
       </c>
-      <c r="B28" t="s" s="21">
-        <v>96</v>
-      </c>
-      <c r="C28" t="s" s="16">
-        <v>85</v>
-      </c>
-      <c r="D28" t="s" s="17">
-        <v>48</v>
-      </c>
-      <c r="E28" t="s" s="17">
-        <v>53</v>
-      </c>
-      <c r="F28" t="s" s="17">
-        <v>52</v>
-      </c>
-      <c r="G28" s="37">
+      <c r="B28" t="s" s="43">
+        <v>106</v>
+      </c>
+      <c r="C28" t="s" s="38">
+        <v>95</v>
+      </c>
+      <c r="D28" t="s" s="39">
+        <v>58</v>
+      </c>
+      <c r="E28" t="s" s="39">
+        <v>63</v>
+      </c>
+      <c r="F28" t="s" s="39">
+        <v>62</v>
+      </c>
+      <c r="G28" s="62">
         <v>2</v>
       </c>
-      <c r="H28" s="37">
+      <c r="H28" s="62">
         <v>1</v>
       </c>
-      <c r="I28" s="37" cm="1">
+      <c r="I28" s="62" cm="1">
         <f t="array" ref="I28">G28*H28</f>
         <v>2</v>
       </c>
@@ -4087,9 +4657,9 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="G3" location="'2. Grille de Scoring - Grille d'!R2C1" tooltip="" display="2. Grille de Scoring"/>
-    <hyperlink ref="H3" location="'2. Grille de Scoring - Grille d'!R2C1" tooltip="" display="2. Grille de Scoring"/>
-    <hyperlink ref="I3" location="'2. Grille de Scoring - Grille d'!R2C1" tooltip="" display="2. Grille de Scoring"/>
+    <hyperlink ref="G3" location="'2. Grille de Scoring - Grille d'!R1C1" tooltip="" display="1: faible&#10;2: moyen&#10;3: critique&#10;Déf: 2. Grille de Scoring"/>
+    <hyperlink ref="H3" location="'2. Grille de Scoring - Grille d'!R1C1" tooltip="" display="1: faible&#10;2: moyen&#10;3: critique&#10;Déf: 2. Grille de Scoring"/>
+    <hyperlink ref="I3" location="'2. Grille de Scoring - Grille d'!R1C1" tooltip="" display="- 1–2: acceptable &#10;- 3–5: remédiation sous 3 mois &#10;- 6–9: correction dans la semaine&#10;Déf: 2. Grille de Scoring"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -4104,305 +4674,331 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:D25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="16.3516" style="38" customWidth="1"/>
-    <col min="2" max="2" width="30.2031" style="38" customWidth="1"/>
-    <col min="3" max="3" width="48.9531" style="38" customWidth="1"/>
-    <col min="4" max="4" width="36.0938" style="38" customWidth="1"/>
-    <col min="5" max="16384" width="16.3516" style="38" customWidth="1"/>
+    <col min="1" max="1" width="16.3516" style="63" customWidth="1"/>
+    <col min="2" max="2" width="30.1719" style="63" customWidth="1"/>
+    <col min="3" max="3" width="49" style="63" customWidth="1"/>
+    <col min="4" max="4" width="36.1719" style="63" customWidth="1"/>
+    <col min="5" max="5" width="16.3516" style="63" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="63" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.6" customHeight="1">
-      <c r="A1" t="s" s="24">
-        <v>98</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="A1" t="s" s="64">
+        <v>13</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="28"/>
     </row>
     <row r="2" ht="20.3" customHeight="1">
-      <c r="A2" t="s" s="39">
-        <v>100</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
+      <c r="A2" t="s" s="66">
+        <v>108</v>
+      </c>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="69"/>
     </row>
     <row r="3" ht="19.2" customHeight="1">
-      <c r="A3" t="s" s="42">
-        <v>101</v>
-      </c>
-      <c r="B3" t="s" s="11">
-        <v>102</v>
-      </c>
-      <c r="C3" t="s" s="11">
-        <v>103</v>
-      </c>
-      <c r="D3" t="s" s="43">
-        <v>104</v>
-      </c>
+      <c r="A3" t="s" s="70">
+        <v>109</v>
+      </c>
+      <c r="B3" t="s" s="33">
+        <v>110</v>
+      </c>
+      <c r="C3" t="s" s="33">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s" s="71">
+        <v>112</v>
+      </c>
+      <c r="E3" s="69"/>
     </row>
     <row r="4" ht="19.2" customHeight="1">
-      <c r="A4" s="44">
+      <c r="A4" s="72">
         <v>1</v>
       </c>
-      <c r="B4" t="s" s="45">
-        <v>105</v>
-      </c>
-      <c r="C4" t="s" s="14">
-        <v>106</v>
-      </c>
-      <c r="D4" t="s" s="46">
-        <v>107</v>
-      </c>
+      <c r="B4" t="s" s="73">
+        <v>113</v>
+      </c>
+      <c r="C4" t="s" s="36">
+        <v>114</v>
+      </c>
+      <c r="D4" t="s" s="74">
+        <v>115</v>
+      </c>
+      <c r="E4" s="69"/>
     </row>
     <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="47">
+      <c r="A5" s="75">
         <v>2</v>
       </c>
-      <c r="B5" t="s" s="48">
-        <v>108</v>
-      </c>
-      <c r="C5" t="s" s="17">
+      <c r="B5" t="s" s="76">
+        <v>116</v>
+      </c>
+      <c r="C5" t="s" s="39">
+        <v>117</v>
+      </c>
+      <c r="D5" t="s" s="77">
+        <v>118</v>
+      </c>
+      <c r="E5" s="69"/>
+    </row>
+    <row r="6" ht="19.3" customHeight="1">
+      <c r="A6" s="78">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s" s="79">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s" s="80">
+        <v>120</v>
+      </c>
+      <c r="D6" t="s" s="81">
+        <v>121</v>
+      </c>
+      <c r="E6" s="69"/>
+    </row>
+    <row r="7" ht="19.65" customHeight="1">
+      <c r="A7" s="82"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="31"/>
+    </row>
+    <row r="8" ht="20.3" customHeight="1">
+      <c r="A8" s="85"/>
+      <c r="B8" t="s" s="86">
+        <v>122</v>
+      </c>
+      <c r="C8" s="87"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="69"/>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" t="s" s="89">
         <v>109</v>
       </c>
-      <c r="D5" t="s" s="49">
+      <c r="B9" t="s" s="90">
         <v>110</v>
       </c>
-    </row>
-    <row r="6" ht="19.3" customHeight="1">
-      <c r="A6" s="50">
+      <c r="C9" t="s" s="32">
+        <v>123</v>
+      </c>
+      <c r="D9" t="s" s="91">
+        <v>112</v>
+      </c>
+      <c r="E9" s="69"/>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="75">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s" s="76">
+        <v>113</v>
+      </c>
+      <c r="C10" t="s" s="39">
+        <v>124</v>
+      </c>
+      <c r="D10" t="s" s="77">
+        <v>125</v>
+      </c>
+      <c r="E10" s="69"/>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="75">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s" s="76">
+        <v>126</v>
+      </c>
+      <c r="C11" t="s" s="39">
+        <v>127</v>
+      </c>
+      <c r="D11" t="s" s="77">
+        <v>128</v>
+      </c>
+      <c r="E11" s="69"/>
+    </row>
+    <row r="12" ht="19.3" customHeight="1">
+      <c r="A12" s="78">
         <v>3</v>
       </c>
-      <c r="B6" t="s" s="51">
+      <c r="B12" t="s" s="79">
+        <v>129</v>
+      </c>
+      <c r="C12" t="s" s="80">
+        <v>130</v>
+      </c>
+      <c r="D12" t="s" s="81">
+        <v>131</v>
+      </c>
+      <c r="E12" s="69"/>
+    </row>
+    <row r="13" ht="19.65" customHeight="1">
+      <c r="A13" s="92"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="31"/>
+    </row>
+    <row r="14" ht="20.3" customHeight="1">
+      <c r="A14" s="85"/>
+      <c r="B14" t="s" s="93">
+        <v>132</v>
+      </c>
+      <c r="C14" s="87"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="69"/>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="94"/>
+      <c r="B15" t="s" s="95">
+        <v>133</v>
+      </c>
+      <c r="C15" s="44"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="69"/>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" t="s" s="89">
+        <v>110</v>
+      </c>
+      <c r="B16" t="s" s="90">
+        <v>109</v>
+      </c>
+      <c r="C16" t="s" s="32">
+        <v>134</v>
+      </c>
+      <c r="D16" s="97"/>
+      <c r="E16" s="69"/>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" t="s" s="98">
+        <v>113</v>
+      </c>
+      <c r="B17" t="s" s="76">
+        <v>135</v>
+      </c>
+      <c r="C17" t="s" s="39">
+        <v>136</v>
+      </c>
+      <c r="D17" s="99"/>
+      <c r="E17" s="69"/>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" t="s" s="100">
+        <v>116</v>
+      </c>
+      <c r="B18" t="s" s="76">
+        <v>137</v>
+      </c>
+      <c r="C18" t="s" s="39">
+        <v>138</v>
+      </c>
+      <c r="D18" s="99"/>
+      <c r="E18" s="69"/>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" t="s" s="101">
+        <v>139</v>
+      </c>
+      <c r="B19" t="s" s="76">
+        <v>140</v>
+      </c>
+      <c r="C19" t="s" s="39">
+        <v>141</v>
+      </c>
+      <c r="D19" s="99"/>
+      <c r="E19" s="69"/>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="102"/>
+      <c r="B20" t="s" s="95">
+        <v>142</v>
+      </c>
+      <c r="C20" s="44"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="69"/>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" t="s" s="89">
+        <v>143</v>
+      </c>
+      <c r="B21" t="s" s="90">
         <v>111</v>
       </c>
-      <c r="C6" t="s" s="52">
+      <c r="C21" t="s" s="32">
+        <v>144</v>
+      </c>
+      <c r="D21" t="s" s="91">
         <v>112</v>
       </c>
-      <c r="D6" t="s" s="53">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" ht="19.65" customHeight="1">
-      <c r="A7" s="54"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-    </row>
-    <row r="8" ht="20.3" customHeight="1">
-      <c r="A8" s="57"/>
-      <c r="B8" t="s" s="58">
-        <v>114</v>
-      </c>
-      <c r="C8" s="59"/>
-      <c r="D8" s="60"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" t="s" s="61">
-        <v>101</v>
-      </c>
-      <c r="B9" t="s" s="62">
-        <v>102</v>
-      </c>
-      <c r="C9" t="s" s="10">
-        <v>115</v>
-      </c>
-      <c r="D9" t="s" s="63">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="47">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s" s="48">
-        <v>105</v>
-      </c>
-      <c r="C10" t="s" s="17">
-        <v>116</v>
-      </c>
-      <c r="D10" t="s" s="49">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="47">
-        <v>2</v>
-      </c>
-      <c r="B11" t="s" s="48">
-        <v>118</v>
-      </c>
-      <c r="C11" t="s" s="17">
-        <v>119</v>
-      </c>
-      <c r="D11" t="s" s="49">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" ht="19.3" customHeight="1">
-      <c r="A12" s="50">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s" s="51">
-        <v>121</v>
-      </c>
-      <c r="C12" t="s" s="52">
-        <v>122</v>
-      </c>
-      <c r="D12" t="s" s="53">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" ht="19.65" customHeight="1">
-      <c r="A13" s="64"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-    </row>
-    <row r="14" ht="20.3" customHeight="1">
-      <c r="A14" s="57"/>
-      <c r="B14" t="s" s="65">
-        <v>124</v>
-      </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="60"/>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="66"/>
-      <c r="B15" t="s" s="67">
-        <v>125</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="68"/>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" t="s" s="61">
-        <v>102</v>
-      </c>
-      <c r="B16" t="s" s="62">
-        <v>101</v>
-      </c>
-      <c r="C16" t="s" s="10">
-        <v>126</v>
-      </c>
-      <c r="D16" s="69"/>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" t="s" s="70">
-        <v>105</v>
-      </c>
-      <c r="B17" t="s" s="48">
-        <v>127</v>
-      </c>
-      <c r="C17" t="s" s="17">
-        <v>128</v>
-      </c>
-      <c r="D17" s="71"/>
-    </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" t="s" s="72">
-        <v>108</v>
-      </c>
-      <c r="B18" t="s" s="48">
-        <v>129</v>
-      </c>
-      <c r="C18" t="s" s="17">
-        <v>130</v>
-      </c>
-      <c r="D18" s="71"/>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" t="s" s="73">
-        <v>131</v>
-      </c>
-      <c r="B19" t="s" s="48">
-        <v>132</v>
-      </c>
-      <c r="C19" t="s" s="17">
-        <v>133</v>
-      </c>
-      <c r="D19" s="71"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="74"/>
-      <c r="B20" t="s" s="67">
-        <v>134</v>
-      </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="68"/>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" t="s" s="61">
-        <v>135</v>
-      </c>
-      <c r="B21" t="s" s="62">
-        <v>103</v>
-      </c>
-      <c r="C21" t="s" s="10">
-        <v>136</v>
-      </c>
-      <c r="D21" t="s" s="63">
-        <v>104</v>
-      </c>
+      <c r="E21" s="69"/>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" t="s" s="75">
-        <v>137</v>
-      </c>
-      <c r="B22" t="s" s="48">
-        <v>138</v>
-      </c>
-      <c r="C22" t="s" s="17">
-        <v>139</v>
-      </c>
-      <c r="D22" t="s" s="49">
-        <v>140</v>
-      </c>
+      <c r="A22" t="s" s="103">
+        <v>145</v>
+      </c>
+      <c r="B22" t="s" s="76">
+        <v>146</v>
+      </c>
+      <c r="C22" t="s" s="39">
+        <v>147</v>
+      </c>
+      <c r="D22" t="s" s="77">
+        <v>148</v>
+      </c>
+      <c r="E22" s="69"/>
     </row>
     <row r="23" ht="20.05" customHeight="1">
-      <c r="A23" t="s" s="76">
-        <v>141</v>
-      </c>
-      <c r="B23" t="s" s="77">
-        <v>142</v>
-      </c>
-      <c r="C23" t="s" s="18">
-        <v>143</v>
-      </c>
-      <c r="D23" t="s" s="78">
-        <v>144</v>
-      </c>
+      <c r="A23" t="s" s="104">
+        <v>149</v>
+      </c>
+      <c r="B23" t="s" s="105">
+        <v>150</v>
+      </c>
+      <c r="C23" t="s" s="40">
+        <v>151</v>
+      </c>
+      <c r="D23" t="s" s="106">
+        <v>152</v>
+      </c>
+      <c r="E23" s="69"/>
     </row>
     <row r="24" ht="23.85" customHeight="1">
-      <c r="A24" t="s" s="76">
-        <v>145</v>
-      </c>
-      <c r="B24" t="s" s="77">
-        <v>146</v>
-      </c>
-      <c r="C24" t="s" s="18">
-        <v>147</v>
-      </c>
-      <c r="D24" t="s" s="78">
-        <v>148</v>
-      </c>
+      <c r="A24" t="s" s="104">
+        <v>153</v>
+      </c>
+      <c r="B24" t="s" s="105">
+        <v>154</v>
+      </c>
+      <c r="C24" t="s" s="40">
+        <v>155</v>
+      </c>
+      <c r="D24" t="s" s="106">
+        <v>156</v>
+      </c>
+      <c r="E24" s="69"/>
     </row>
     <row r="25" ht="32.35" customHeight="1">
-      <c r="A25" t="s" s="79">
-        <v>149</v>
-      </c>
-      <c r="B25" t="s" s="80">
-        <v>150</v>
-      </c>
-      <c r="C25" t="s" s="81">
-        <v>151</v>
-      </c>
-      <c r="D25" t="s" s="82">
-        <v>152</v>
-      </c>
+      <c r="A25" t="s" s="107">
+        <v>157</v>
+      </c>
+      <c r="B25" t="s" s="108">
+        <v>158</v>
+      </c>
+      <c r="C25" t="s" s="109">
+        <v>159</v>
+      </c>
+      <c r="D25" t="s" s="110">
+        <v>160</v>
+      </c>
+      <c r="E25" s="111"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4426,436 +5022,436 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="7.8125" style="83" customWidth="1"/>
-    <col min="2" max="2" width="16.3516" style="83" customWidth="1"/>
-    <col min="3" max="3" width="12.1953" style="83" customWidth="1"/>
-    <col min="4" max="4" width="27.5703" style="83" customWidth="1"/>
-    <col min="5" max="5" width="23.5703" style="83" customWidth="1"/>
-    <col min="6" max="6" width="30.5234" style="83" customWidth="1"/>
-    <col min="7" max="8" width="16.3516" style="83" customWidth="1"/>
-    <col min="9" max="16384" width="16.3516" style="83" customWidth="1"/>
+    <col min="1" max="1" width="7.85156" style="112" customWidth="1"/>
+    <col min="2" max="2" width="16.3516" style="112" customWidth="1"/>
+    <col min="3" max="3" width="12.1719" style="112" customWidth="1"/>
+    <col min="4" max="4" width="27.5" style="112" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="112" customWidth="1"/>
+    <col min="6" max="6" width="30.5" style="112" customWidth="1"/>
+    <col min="7" max="8" width="16.3516" style="112" customWidth="1"/>
+    <col min="9" max="16384" width="16.3516" style="112" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.65" customHeight="1">
-      <c r="A1" t="s" s="7">
-        <v>154</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="A1" t="s" s="26">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="113"/>
     </row>
     <row r="2" ht="44.25" customHeight="1">
-      <c r="A2" t="s" s="84">
-        <v>156</v>
-      </c>
-      <c r="B2" t="s" s="84">
-        <v>157</v>
-      </c>
-      <c r="C2" t="s" s="84">
-        <v>158</v>
-      </c>
-      <c r="D2" t="s" s="84">
-        <v>159</v>
-      </c>
-      <c r="E2" t="s" s="84">
-        <v>160</v>
-      </c>
-      <c r="F2" t="s" s="84">
-        <v>161</v>
-      </c>
-      <c r="G2" t="s" s="84">
+      <c r="A2" t="s" s="114">
         <v>162</v>
       </c>
-      <c r="H2" t="s" s="84">
+      <c r="B2" t="s" s="114">
         <v>163</v>
       </c>
+      <c r="C2" t="s" s="114">
+        <v>164</v>
+      </c>
+      <c r="D2" t="s" s="114">
+        <v>165</v>
+      </c>
+      <c r="E2" t="s" s="114">
+        <v>166</v>
+      </c>
+      <c r="F2" t="s" s="114">
+        <v>167</v>
+      </c>
+      <c r="G2" t="s" s="114">
+        <v>168</v>
+      </c>
+      <c r="H2" t="s" s="114">
+        <v>169</v>
+      </c>
     </row>
     <row r="3" ht="41.25" customHeight="1">
-      <c r="A3" t="s" s="25">
-        <v>37</v>
-      </c>
-      <c r="B3" t="s" s="26">
-        <v>38</v>
-      </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="87"/>
-      <c r="H3" t="s" s="88">
-        <v>164</v>
+      <c r="A3" t="s" s="50">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s" s="51">
+        <v>48</v>
+      </c>
+      <c r="C3" s="115"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="117"/>
+      <c r="H3" t="s" s="118">
+        <v>170</v>
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
-      <c r="A4" s="30">
+      <c r="A4" s="55">
         <v>1</v>
       </c>
-      <c r="B4" t="s" s="31">
-        <v>45</v>
-      </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
+      <c r="B4" t="s" s="56">
+        <v>55</v>
+      </c>
+      <c r="C4" s="119"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
     </row>
     <row r="5" ht="23.85" customHeight="1">
-      <c r="A5" s="90">
+      <c r="A5" s="120">
         <v>5</v>
       </c>
-      <c r="B5" t="s" s="91">
-        <v>55</v>
-      </c>
-      <c r="C5" s="92">
+      <c r="B5" t="s" s="121">
+        <v>65</v>
+      </c>
+      <c r="C5" s="122">
         <v>6</v>
       </c>
-      <c r="D5" t="s" s="18">
-        <v>165</v>
-      </c>
-      <c r="E5" t="s" s="18">
-        <v>166</v>
-      </c>
-      <c r="F5" t="s" s="18">
-        <v>167</v>
-      </c>
-      <c r="G5" t="s" s="93">
-        <v>145</v>
-      </c>
-      <c r="H5" s="94">
+      <c r="D5" t="s" s="40">
+        <v>171</v>
+      </c>
+      <c r="E5" t="s" s="40">
+        <v>172</v>
+      </c>
+      <c r="F5" t="s" s="40">
+        <v>173</v>
+      </c>
+      <c r="G5" t="s" s="123">
+        <v>153</v>
+      </c>
+      <c r="H5" s="124">
         <v>2</v>
       </c>
     </row>
     <row r="6" ht="23.85" customHeight="1">
-      <c r="A6" s="90">
+      <c r="A6" s="120">
         <v>5</v>
       </c>
-      <c r="B6" t="s" s="91">
-        <v>55</v>
-      </c>
-      <c r="C6" s="92">
+      <c r="B6" t="s" s="121">
+        <v>65</v>
+      </c>
+      <c r="C6" s="122">
         <v>6</v>
       </c>
-      <c r="D6" t="s" s="18">
-        <v>168</v>
-      </c>
-      <c r="E6" t="s" s="18">
-        <v>169</v>
-      </c>
-      <c r="F6" t="s" s="18">
-        <v>170</v>
-      </c>
-      <c r="G6" t="s" s="93">
-        <v>145</v>
-      </c>
-      <c r="H6" s="94">
+      <c r="D6" t="s" s="40">
+        <v>174</v>
+      </c>
+      <c r="E6" t="s" s="40">
+        <v>175</v>
+      </c>
+      <c r="F6" t="s" s="40">
+        <v>176</v>
+      </c>
+      <c r="G6" t="s" s="123">
+        <v>153</v>
+      </c>
+      <c r="H6" s="124">
         <v>2</v>
       </c>
     </row>
     <row r="7" ht="32.05" customHeight="1">
-      <c r="A7" s="90">
+      <c r="A7" s="120">
         <v>6</v>
       </c>
-      <c r="B7" t="s" s="91">
-        <v>59</v>
-      </c>
-      <c r="C7" s="92">
+      <c r="B7" t="s" s="121">
+        <v>69</v>
+      </c>
+      <c r="C7" s="122">
         <v>6</v>
       </c>
-      <c r="D7" t="s" s="18">
-        <v>171</v>
-      </c>
-      <c r="E7" t="s" s="18">
-        <v>172</v>
-      </c>
-      <c r="F7" t="s" s="18">
-        <v>173</v>
-      </c>
-      <c r="G7" t="s" s="93">
-        <v>141</v>
-      </c>
-      <c r="H7" s="94">
+      <c r="D7" t="s" s="40">
+        <v>177</v>
+      </c>
+      <c r="E7" t="s" s="40">
+        <v>178</v>
+      </c>
+      <c r="F7" t="s" s="40">
+        <v>179</v>
+      </c>
+      <c r="G7" t="s" s="123">
+        <v>149</v>
+      </c>
+      <c r="H7" s="124">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="32.05" customHeight="1">
-      <c r="A8" s="90">
+      <c r="A8" s="120">
         <v>6</v>
       </c>
-      <c r="B8" t="s" s="91">
-        <v>59</v>
-      </c>
-      <c r="C8" s="92">
+      <c r="B8" t="s" s="121">
+        <v>69</v>
+      </c>
+      <c r="C8" s="122">
         <v>6</v>
       </c>
-      <c r="D8" t="s" s="18">
-        <v>174</v>
-      </c>
-      <c r="E8" t="s" s="18">
-        <v>175</v>
-      </c>
-      <c r="F8" t="s" s="18">
-        <v>176</v>
-      </c>
-      <c r="G8" t="s" s="93">
-        <v>141</v>
-      </c>
-      <c r="H8" s="94">
+      <c r="D8" t="s" s="40">
+        <v>180</v>
+      </c>
+      <c r="E8" t="s" s="40">
+        <v>181</v>
+      </c>
+      <c r="F8" t="s" s="40">
+        <v>182</v>
+      </c>
+      <c r="G8" t="s" s="123">
+        <v>149</v>
+      </c>
+      <c r="H8" s="124">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="32.05" customHeight="1">
-      <c r="A9" s="90">
+      <c r="A9" s="120">
         <v>8</v>
       </c>
-      <c r="B9" t="s" s="91">
-        <v>64</v>
-      </c>
-      <c r="C9" s="92">
+      <c r="B9" t="s" s="121">
+        <v>74</v>
+      </c>
+      <c r="C9" s="122">
         <v>6</v>
       </c>
-      <c r="D9" t="s" s="18">
-        <v>174</v>
-      </c>
-      <c r="E9" t="s" s="18">
+      <c r="D9" t="s" s="40">
+        <v>180</v>
+      </c>
+      <c r="E9" t="s" s="40">
+        <v>183</v>
+      </c>
+      <c r="F9" t="s" s="40">
+        <v>184</v>
+      </c>
+      <c r="G9" t="s" s="123">
+        <v>149</v>
+      </c>
+      <c r="H9" s="124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="32.05" customHeight="1">
+      <c r="A10" s="120">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s" s="121">
+        <v>74</v>
+      </c>
+      <c r="C10" s="122">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s" s="40">
+        <v>185</v>
+      </c>
+      <c r="E10" t="s" s="40">
+        <v>186</v>
+      </c>
+      <c r="F10" t="s" s="40">
+        <v>184</v>
+      </c>
+      <c r="G10" t="s" s="123">
+        <v>149</v>
+      </c>
+      <c r="H10" s="124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="44.05" customHeight="1">
+      <c r="A11" s="120">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s" s="121">
+        <v>85</v>
+      </c>
+      <c r="C11" s="122">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s" s="40">
+        <v>180</v>
+      </c>
+      <c r="E11" t="s" s="40">
+        <v>187</v>
+      </c>
+      <c r="F11" t="s" s="40">
+        <v>188</v>
+      </c>
+      <c r="G11" t="s" s="123">
+        <v>149</v>
+      </c>
+      <c r="H11" s="124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" ht="44.05" customHeight="1">
+      <c r="A12" s="120">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s" s="121">
+        <v>85</v>
+      </c>
+      <c r="C12" s="122">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s" s="40">
         <v>177</v>
       </c>
-      <c r="F9" t="s" s="18">
-        <v>178</v>
-      </c>
-      <c r="G9" t="s" s="93">
-        <v>141</v>
-      </c>
-      <c r="H9" s="94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="32.05" customHeight="1">
-      <c r="A10" s="90">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s" s="91">
-        <v>64</v>
-      </c>
-      <c r="C10" s="92">
+      <c r="E12" t="s" s="40">
+        <v>189</v>
+      </c>
+      <c r="F12" t="s" s="40">
+        <v>190</v>
+      </c>
+      <c r="G12" t="s" s="123">
+        <v>149</v>
+      </c>
+      <c r="H12" s="124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" ht="32.05" customHeight="1">
+      <c r="A13" s="120">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s" s="121">
+        <v>89</v>
+      </c>
+      <c r="C13" s="122">
         <v>6</v>
       </c>
-      <c r="D10" t="s" s="18">
-        <v>179</v>
-      </c>
-      <c r="E10" t="s" s="18">
-        <v>180</v>
-      </c>
-      <c r="F10" t="s" s="18">
-        <v>178</v>
-      </c>
-      <c r="G10" t="s" s="93">
-        <v>141</v>
-      </c>
-      <c r="H10" s="94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="44.05" customHeight="1">
-      <c r="A11" s="90">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s" s="91">
-        <v>75</v>
-      </c>
-      <c r="C11" s="92">
+      <c r="D13" t="s" s="40">
+        <v>177</v>
+      </c>
+      <c r="E13" t="s" s="40">
+        <v>191</v>
+      </c>
+      <c r="F13" t="s" s="40">
+        <v>192</v>
+      </c>
+      <c r="G13" t="s" s="123">
+        <v>149</v>
+      </c>
+      <c r="H13" s="124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" ht="32.05" customHeight="1">
+      <c r="A14" s="120">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s" s="121">
+        <v>89</v>
+      </c>
+      <c r="C14" s="122">
         <v>6</v>
       </c>
-      <c r="D11" t="s" s="18">
-        <v>174</v>
-      </c>
-      <c r="E11" t="s" s="18">
-        <v>181</v>
-      </c>
-      <c r="F11" t="s" s="18">
-        <v>182</v>
-      </c>
-      <c r="G11" t="s" s="93">
-        <v>141</v>
-      </c>
-      <c r="H11" s="94">
+      <c r="D14" t="s" s="40">
+        <v>193</v>
+      </c>
+      <c r="E14" t="s" s="40">
+        <v>194</v>
+      </c>
+      <c r="F14" t="s" s="40">
+        <v>192</v>
+      </c>
+      <c r="G14" t="s" s="123">
+        <v>149</v>
+      </c>
+      <c r="H14" s="124">
         <v>2</v>
       </c>
     </row>
-    <row r="12" ht="44.05" customHeight="1">
-      <c r="A12" s="90">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s" s="91">
-        <v>75</v>
-      </c>
-      <c r="C12" s="92">
+    <row r="15" ht="32.05" customHeight="1">
+      <c r="A15" s="120">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s" s="121">
+        <v>91</v>
+      </c>
+      <c r="C15" s="122">
         <v>6</v>
       </c>
-      <c r="D12" t="s" s="18">
-        <v>171</v>
-      </c>
-      <c r="E12" t="s" s="18">
-        <v>183</v>
-      </c>
-      <c r="F12" t="s" s="18">
-        <v>184</v>
-      </c>
-      <c r="G12" t="s" s="93">
-        <v>141</v>
-      </c>
-      <c r="H12" s="94">
+      <c r="D15" t="s" s="40">
+        <v>195</v>
+      </c>
+      <c r="E15" t="s" s="40">
+        <v>196</v>
+      </c>
+      <c r="F15" t="s" s="40">
+        <v>197</v>
+      </c>
+      <c r="G15" t="s" s="123">
+        <v>149</v>
+      </c>
+      <c r="H15" s="124">
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="32.05" customHeight="1">
-      <c r="A13" s="90">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s" s="91">
-        <v>79</v>
-      </c>
-      <c r="C13" s="92">
+    <row r="16" ht="32.05" customHeight="1">
+      <c r="A16" s="120">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s" s="121">
+        <v>91</v>
+      </c>
+      <c r="C16" s="122">
         <v>6</v>
       </c>
-      <c r="D13" t="s" s="18">
-        <v>171</v>
-      </c>
-      <c r="E13" t="s" s="18">
-        <v>185</v>
-      </c>
-      <c r="F13" t="s" s="18">
-        <v>186</v>
-      </c>
-      <c r="G13" t="s" s="93">
-        <v>141</v>
-      </c>
-      <c r="H13" s="94">
+      <c r="D16" t="s" s="40">
+        <v>177</v>
+      </c>
+      <c r="E16" t="s" s="40">
+        <v>198</v>
+      </c>
+      <c r="F16" t="s" s="40">
+        <v>199</v>
+      </c>
+      <c r="G16" t="s" s="123">
+        <v>149</v>
+      </c>
+      <c r="H16" s="124">
         <v>2</v>
       </c>
     </row>
-    <row r="14" ht="32.05" customHeight="1">
-      <c r="A14" s="90">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s" s="91">
-        <v>79</v>
-      </c>
-      <c r="C14" s="92">
-        <v>6</v>
-      </c>
-      <c r="D14" t="s" s="18">
-        <v>187</v>
-      </c>
-      <c r="E14" t="s" s="18">
-        <v>188</v>
-      </c>
-      <c r="F14" t="s" s="18">
-        <v>186</v>
-      </c>
-      <c r="G14" t="s" s="93">
-        <v>141</v>
-      </c>
-      <c r="H14" s="94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" ht="32.05" customHeight="1">
-      <c r="A15" s="90">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s" s="91">
-        <v>81</v>
-      </c>
-      <c r="C15" s="92">
-        <v>6</v>
-      </c>
-      <c r="D15" t="s" s="18">
-        <v>189</v>
-      </c>
-      <c r="E15" t="s" s="18">
-        <v>190</v>
-      </c>
-      <c r="F15" t="s" s="18">
-        <v>191</v>
-      </c>
-      <c r="G15" t="s" s="93">
-        <v>141</v>
-      </c>
-      <c r="H15" s="94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" ht="32.05" customHeight="1">
-      <c r="A16" s="90">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s" s="91">
-        <v>81</v>
-      </c>
-      <c r="C16" s="92">
-        <v>6</v>
-      </c>
-      <c r="D16" t="s" s="18">
-        <v>171</v>
-      </c>
-      <c r="E16" t="s" s="18">
-        <v>192</v>
-      </c>
-      <c r="F16" t="s" s="18">
-        <v>193</v>
-      </c>
-      <c r="G16" t="s" s="93">
-        <v>141</v>
-      </c>
-      <c r="H16" s="94">
-        <v>2</v>
-      </c>
-    </row>
     <row r="17" ht="44.05" customHeight="1">
-      <c r="A17" s="90">
+      <c r="A17" s="120">
         <v>7</v>
       </c>
-      <c r="B17" t="s" s="91">
-        <v>62</v>
-      </c>
-      <c r="C17" s="92">
+      <c r="B17" t="s" s="121">
+        <v>72</v>
+      </c>
+      <c r="C17" s="122">
         <v>4</v>
       </c>
-      <c r="D17" t="s" s="18">
-        <v>194</v>
-      </c>
-      <c r="E17" t="s" s="18">
-        <v>195</v>
-      </c>
-      <c r="F17" t="s" s="18">
-        <v>196</v>
-      </c>
-      <c r="G17" t="s" s="18">
-        <v>197</v>
-      </c>
-      <c r="H17" s="94">
+      <c r="D17" t="s" s="40">
+        <v>200</v>
+      </c>
+      <c r="E17" t="s" s="40">
+        <v>201</v>
+      </c>
+      <c r="F17" t="s" s="40">
+        <v>202</v>
+      </c>
+      <c r="G17" t="s" s="40">
+        <v>203</v>
+      </c>
+      <c r="H17" s="124">
         <v>3</v>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" t="s" s="95">
-        <v>198</v>
-      </c>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
+      <c r="A18" t="s" s="125">
+        <v>204</v>
+      </c>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="126"/>
+      <c r="H18" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="2">
